--- a/bookkeeping_template.xlsx
+++ b/bookkeeping_template.xlsx
@@ -11,16 +11,18 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Setup" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Transactions" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Monthly Dashboard" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Quarterly Dashboard" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Yearly Dashboard" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="5-Year Dashboard" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Income Breakdown" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Expense Breakdown" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Profit &amp; Loss Summary" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Tax Summary" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Category Trends" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Notes &amp; Legend" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Business Health Dashboard" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Monthly Dashboard" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Quarterly Dashboard" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Yearly Dashboard" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="5-Year Dashboard" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Income Breakdown" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Expense Breakdown" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Profit &amp; Loss Summary" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Tax Summary" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Account Balance" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Category Trends" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Notes &amp; Legend" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,30 +34,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="146">
   <si>
     <t xml:space="preserve">How to Use This Bookkeeping Dashboard</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open the 'Setup' tab first. Confirm your income/expense categories, tax rate, and profit goals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Log every transaction in the 'Transactions' tab — Date, Type (Income/Expense), Category, Description, Amount, and Tax Collected. Use the dropdowns for Type and Category.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. The 'Monthly Dashboard', 'Quarterly Dashboard', 'Yearly Dashboard', and '5-Year Dashboard' tabs update automatically — just change the Year/Month/Quarter selector cells (yellow) at the top of each tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. 'Income Breakdown' and 'Expense Breakdown' show all-time and current-year totals by category with charts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. 'Profit &amp; Loss Summary' shows one row per year; 'Tax Summary' shows tax collected by month/quarter/year; 'Category Trends' shows a 12-month trend per category.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Only edit yellow (input) or white cells. Green-header and formula cells update automatically — do not overwrite them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. To log more than 100 transactions, select the last formatted row and copy it downward; formulas will carry over.</t>
+    <t xml:space="preserve">1. Open the 'Setup' tab first. Confirm your income/expense categories, tax rate, profit goals, and starting bank balance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Log every transaction in the 'Transactions' tab — Date, Type (Income/Expense), Category, Description, Amount, and Tax Collected. Use the dropdowns for Type and Category; income/expense rows are color-coded automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Check the 'Business Health Dashboard' for an at-a-glance view of cash on hand, YTD profit, margin, growth, cash runway, goal progress, top categories, and a Business Health Score.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. The 'Monthly Dashboard', 'Quarterly Dashboard', 'Yearly Dashboard', and '5-Year Dashboard' tabs update automatically — just change the Year/Month/Quarter selector cells (yellow) at the top of each tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. 'Income Breakdown' and 'Expense Breakdown' show all-time and current-year totals by category with charts and data bars.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. 'Profit &amp; Loss Summary' shows one row per year with year-over-year growth; 'Tax Summary' shows tax collected by month; 'Account Balance' tracks your running cash balance and reconciles against your bank statement; 'Category Trends' shows a 12-month heatmap per category.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Only edit yellow (input) or white cells. Green-header and formula cells update automatically — do not overwrite them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. To log more than 100 transactions, select the last formatted row and copy it downward; formulas will carry over.</t>
   </si>
   <si>
     <t xml:space="preserve">Prepared for {{CLIENT_NAME}} ({{NICHE}}). Amounts are in {{CURRENCY}}.</t>
@@ -82,6 +87,9 @@
     <t xml:space="preserve">Annual Profit Goal ({{CURRENCY}})</t>
   </si>
   <si>
+    <t xml:space="preserve">Starting Bank Balance ({{CURRENCY}})</t>
+  </si>
+  <si>
     <t xml:space="preserve">Income Categories</t>
   </si>
   <si>
@@ -160,6 +168,60 @@
     <t xml:space="preserve">Month</t>
   </si>
   <si>
+    <t xml:space="preserve">{{CLIENT_NAME}} — Business Health Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{NICHE}} — your business at a glance, figures in {{CURRENCY}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash on Hand ({{CURRENCY}})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YTD Net Profit ({{CURRENCY}})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit Margin (YTD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YoY Income Growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goal Progress — YTD Net Profit vs Annual Goal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Category This Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Health Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin Score (30%+ margin = 100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth Score (-20% to +20% mapped to 0-100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runway Score (6+ months = 100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Health Score (0-100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methodology: each sub-score is a simple linear scale between the thresholds shown (e.g. Margin Score reaches 100 once Profit Margin hits 30%). This is a rule-of-thumb indicator, not professional financial advice.</t>
+  </si>
+  <si>
     <t xml:space="preserve">{{CLIENT_NAME}} — Monthly Dashboard</t>
   </si>
   <si>
@@ -322,6 +384,36 @@
     <t xml:space="preserve">Annual Total</t>
   </si>
   <si>
+    <t xml:space="preserve">{{CLIENT_NAME}} — Account Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting Balance ({{CURRENCY}})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Balance ({{CURRENCY}})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statement Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Statement Balance ({{CURRENCY}})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Book Balance as of Statement Date ({{CURRENCY}})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference ({{CURRENCY}})</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ending Balance by Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ending Balance</t>
+  </si>
+  <si>
     <t xml:space="preserve">{{CLIENT_NAME}} — Category Trends</t>
   </si>
   <si>
@@ -343,7 +435,7 @@
     <t xml:space="preserve">Yellow cells</t>
   </si>
   <si>
-    <t xml:space="preserve">Input cells — change these (Year, Quarter, Month, Tax Rate, Goals).</t>
+    <t xml:space="preserve">Input cells — change these (Year, Quarter, Month, Tax Rate, Goals, Starting Balance).</t>
   </si>
   <si>
     <t xml:space="preserve">White cells with borders</t>
@@ -362,18 +454,37 @@
   </si>
   <si>
     <t xml:space="preserve">Calculated automatically from the Transactions tab — do not overwrite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light green / light red rows (Transactions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automatic color coding — green rows are Income, red rows are Expense.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colored bars inside cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data bars on breakdown and balance tables — longer bar = larger amount, for at-a-glance scanning.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red-yellow-green shading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Color scales on YoY Growth, Category Trends, and the Business Health Score — red is low, green is high.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -469,6 +580,13 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -486,13 +604,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -523,7 +634,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEFF5EC"/>
-        <bgColor rgb="FFFFFDE7"/>
+        <bgColor rgb="FFEAF7EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -576,7 +687,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -653,7 +764,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -665,16 +804,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -686,6 +825,22 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAF7EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDEEEE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -707,7 +862,7 @@
       <rgbColor rgb="FF93A9CE"/>
       <rgbColor rgb="FFAB4744"/>
       <rgbColor rgb="FFFFFDE7"/>
-      <rgbColor rgb="FFEFF5EC"/>
+      <rgbColor rgb="FFEAF7EC"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFDC853E"/>
       <rgbColor rgb="FF4672A8"/>
@@ -721,9 +876,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFEFF5EC"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFDEEEE"/>
       <rgbColor rgb="FFB8CD97"/>
       <rgbColor rgb="FFD09493"/>
       <rgbColor rgb="FF8064A2"/>
@@ -1286,11 +1441,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="91451646"/>
-        <c:axId val="78874773"/>
+        <c:axId val="44485420"/>
+        <c:axId val="26811196"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="91451646"/>
+        <c:axId val="44485420"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1322,7 +1477,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78874773"/>
+        <c:crossAx val="26811196"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1330,7 +1485,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78874773"/>
+        <c:axId val="26811196"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1406,7 +1561,341 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91451646"/>
+        <c:crossAx val="44485420"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Cash Balance Over Time — Selected Year</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Account Balance'!B14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ending Balance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Account Balance'!$A$15:$A$26</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Account Balance'!$B$15:$B$26</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="21007547"/>
+        <c:axId val="89725098"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="21007547"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="89725098"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="89725098"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="21007547"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2099,11 +2588,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="2963199"/>
-        <c:axId val="66442885"/>
+        <c:axId val="55475747"/>
+        <c:axId val="91034759"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2963199"/>
+        <c:axId val="55475747"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2135,7 +2624,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66442885"/>
+        <c:crossAx val="91034759"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2143,7 +2632,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66442885"/>
+        <c:axId val="91034759"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2219,7 +2708,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2963199"/>
+        <c:crossAx val="55475747"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2588,11 +3077,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="15368455"/>
-        <c:axId val="42613272"/>
+        <c:axId val="41076862"/>
+        <c:axId val="57819110"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="15368455"/>
+        <c:axId val="41076862"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2624,7 +3113,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42613272"/>
+        <c:crossAx val="57819110"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2632,7 +3121,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="42613272"/>
+        <c:axId val="57819110"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2708,7 +3197,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15368455"/>
+        <c:crossAx val="41076862"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2945,11 +3434,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="91913859"/>
-        <c:axId val="11974357"/>
+        <c:axId val="51836746"/>
+        <c:axId val="28599433"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="91913859"/>
+        <c:axId val="51836746"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2981,7 +3470,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11974357"/>
+        <c:crossAx val="28599433"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2989,7 +3478,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11974357"/>
+        <c:axId val="28599433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3065,7 +3554,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91913859"/>
+        <c:crossAx val="51836746"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3452,11 +3941,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="66169558"/>
-        <c:axId val="71067086"/>
+        <c:axId val="85555836"/>
+        <c:axId val="11949451"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66169558"/>
+        <c:axId val="85555836"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3488,7 +3977,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71067086"/>
+        <c:crossAx val="11949451"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3496,7 +3985,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71067086"/>
+        <c:axId val="11949451"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3572,7 +4061,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66169558"/>
+        <c:crossAx val="85555836"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4676,11 +5165,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="90208918"/>
-        <c:axId val="28673610"/>
+        <c:axId val="60078730"/>
+        <c:axId val="59511018"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="90208918"/>
+        <c:axId val="60078730"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4712,7 +5201,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28673610"/>
+        <c:crossAx val="59511018"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4720,7 +5209,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28673610"/>
+        <c:axId val="59511018"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4762,7 +5251,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90208918"/>
+        <c:crossAx val="60078730"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5096,8 +5585,8 @@
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>447840</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>58320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5105,7 +5594,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8759880" y="762120"/>
+        <a:off x="9334440" y="762120"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5142,6 +5631,41 @@
       <xdr:xfrm>
         <a:off x="3603600" y="762120"/>
         <a:ext cx="5039640" cy="2699640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>447840</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="7870680" y="2562120"/>
+        <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5436,9 +5960,21 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -5449,7 +5985,7 @@
       <c r="H12" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A5:H5"/>
@@ -5458,6 +5994,7 @@
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A12:H12"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5475,15 +6012,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5495,7 +6032,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -5507,33 +6044,254 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>91</v>
+        <v>105</v>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Cost of Goods")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Cost of Goods",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Shipping Costs")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Shipping Costs",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Marketing")</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Marketing",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Software &amp; Tools")</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Software &amp; Tools",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Fees &amp; Commissions")</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Fees &amp; Commissions",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Office Supplies")</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Office Supplies",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Rent")</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Rent",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Utilities")</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Utilities",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Other Expense")</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Other Expense",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6:C14">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="1" minLength="10" maxLength="90">
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFC0504D"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A572D43F-A089-4310-AEED-F4F2A5D9BCDF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A572D43F-A089-4310-AEED-F4F2A5D9BCDF}">
+            <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:negativeFillColor rgb="FFC0504D"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B6:C14</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>93</v>
+        <v>113</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5553,13 +6311,17 @@
         <f aca="false">B6-C6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="28" t="n">
         <f aca="false">IFERROR(D6/B6,0)</f>
         <v>0</v>
       </c>
       <c r="F6" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A6)</f>
         <v>0</v>
+      </c>
+      <c r="G6" s="10" t="str">
+        <f aca="false">"n/a"</f>
+        <v>n/a</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5579,12 +6341,16 @@
         <f aca="false">B7-C7</f>
         <v>0</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="28" t="n">
         <f aca="false">IFERROR(D7/B7,0)</f>
         <v>0</v>
       </c>
       <c r="F7" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A7)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <f aca="false">IFERROR((B7-B6)/B6,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5605,12 +6371,16 @@
         <f aca="false">B8-C8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="28" t="n">
         <f aca="false">IFERROR(D8/B8,0)</f>
         <v>0</v>
       </c>
       <c r="F8" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A8)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <f aca="false">IFERROR((B8-B7)/B7,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5631,12 +6401,16 @@
         <f aca="false">B9-C9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="28" t="n">
         <f aca="false">IFERROR(D9/B9,0)</f>
         <v>0</v>
       </c>
       <c r="F9" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A9)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <f aca="false">IFERROR((B9-B8)/B8,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5657,12 +6431,16 @@
         <f aca="false">B10-C10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="28" t="n">
         <f aca="false">IFERROR(D10/B10,0)</f>
         <v>0</v>
       </c>
       <c r="F10" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A10)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <f aca="false">IFERROR((B10-B9)/B9,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5683,12 +6461,16 @@
         <f aca="false">B11-C11</f>
         <v>0</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="28" t="n">
         <f aca="false">IFERROR(D11/B11,0)</f>
         <v>0</v>
       </c>
       <c r="F11" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A11)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <f aca="false">IFERROR((B11-B10)/B10,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5709,12 +6491,16 @@
         <f aca="false">B12-C12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="28" t="n">
         <f aca="false">IFERROR(D12/B12,0)</f>
         <v>0</v>
       </c>
       <c r="F12" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A12)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <f aca="false">IFERROR((B12-B11)/B11,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5735,12 +6521,16 @@
         <f aca="false">B13-C13</f>
         <v>0</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="28" t="n">
         <f aca="false">IFERROR(D13/B13,0)</f>
         <v>0</v>
       </c>
       <c r="F13" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A13)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="28" t="n">
+        <f aca="false">IFERROR((B13-B12)/B12,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5761,12 +6551,16 @@
         <f aca="false">B14-C14</f>
         <v>0</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="28" t="n">
         <f aca="false">IFERROR(D14/B14,0)</f>
         <v>0</v>
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A14)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <f aca="false">IFERROR((B14-B13)/B13,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5787,12 +6581,212 @@
         <f aca="false">B15-C15</f>
         <v>0</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="28" t="n">
         <f aca="false">IFERROR(D15/B15,0)</f>
         <v>0</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A15)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <f aca="false">IFERROR((B15-B14)/B14,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G7:G15">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="30" t="n">
+        <f aca="false">SUM(B6:B17)</f>
         <v>0</v>
       </c>
     </row>
@@ -5812,20 +6806,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5837,7 +6831,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -5847,136 +6841,188 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="n">
+        <f aca="false">Setup!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="B4" s="17" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income")-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,2)</f>
-        <v>0</v>
+      <c r="A7" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,3)</f>
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="B8" s="31" t="n">
+        <f aca="true">TODAY()</f>
+        <v>46248</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,4)</f>
+        <v>121</v>
+      </c>
+      <c r="B9" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="B10" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,5)</f>
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;$B$8)-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;$B$8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,7)</f>
+      <c r="A11" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="30" t="n">
+        <f aca="false">B9-B10</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,8)</f>
-        <v>0</v>
+      <c r="A13" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>2026</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,9)</f>
-        <v>0</v>
+      <c r="A14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B15" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,10)</f>
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,1+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,1+1,1)-1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B16" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,11)</f>
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,2+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,2+1,1)-1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,12)</f>
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,3+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,3+1,1)-1))</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="9" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,4+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,4+1,1)-1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,5+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,5+1,1)-1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,6+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,6+1,1)-1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="9" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,7+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,7+1,1)-1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="9" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,8+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,8+1,1)-1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="23" t="n">
-        <f aca="false">SUM(B6:B17)</f>
+      <c r="B23" s="9" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,9+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,9+1,1)-1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="9" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,10+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,10+1,1)-1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="9" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,11+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,11+1,1)-1))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="9" t="n">
+        <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,12+1,1)-1))-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$A$3:$A$102,"&lt;="&amp;(DATE($D$13,12+1,1)-1))</f>
         <v>0</v>
       </c>
     </row>
@@ -5985,6 +7031,14 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>B11=0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>B11&lt;&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5996,7 +7050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -6010,7 +7064,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6022,7 +7076,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -6034,7 +7088,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>2026</v>
@@ -6042,54 +7096,54 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C6" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Sales Revenue",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6142,10 +7196,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C7" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Shipping Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6198,10 +7252,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C8" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Custom Orders",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6254,10 +7308,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C9" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Wholesale",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6310,10 +7364,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C10" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Other Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6366,10 +7420,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Cost of Goods",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6422,10 +7476,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C12" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Shipping Costs",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6478,10 +7532,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C13" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Marketing",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6534,10 +7588,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Software &amp; Tools",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6590,10 +7644,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C15" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Fees &amp; Commissions",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6646,10 +7700,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C16" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Office Supplies",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6702,10 +7756,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C17" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Rent",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6758,10 +7812,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C18" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Utilities",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6814,10 +7868,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C19" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Other Expense",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -6873,6 +7927,16 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
+  <conditionalFormatting sqref="C6:N19">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF4C7A47"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -6883,12 +7947,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -6897,7 +7961,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6909,54 +7973,78 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>103</v>
+        <v>132</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>105</v>
+        <v>134</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>107</v>
+        <v>136</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3"/>
+        <v>138</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6981,7 +8069,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6993,7 +8081,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -7005,15 +8093,15 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>0.1</v>
@@ -7021,7 +8109,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>2000</v>
@@ -7029,134 +8117,142 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">B5*12</f>
         <v>24000</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C19" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C20" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C21" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C22" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -7193,7 +8289,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7205,28 +8301,28 @@
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8833,6 +9929,14 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <conditionalFormatting sqref="A3:H102">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$B3="Income"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>$B3="Expense"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B3:B102" type="list">
       <formula1>"Income,Expense"</formula1>
@@ -8858,6 +9962,254 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="n">
+        <f aca="false">'Account Balance'!B4</f>
+        <v>0</v>
+      </c>
+      <c r="B6" s="17" t="n">
+        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3)-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$G$3:$G$102,$B$3)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <f aca="false">IFERROR(B6/SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <f aca="false">IFERROR((SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3)-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3-1))/SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3-1),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <f aca="false">IFERROR(A6/(SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$G$3:$G$102,$B$3)/12),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="20" t="n">
+        <f aca="false">IFERROR(B6/Setup!$B$6,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="10" t="str">
+        <f aca="false">INDEX('Income Breakdown'!A6:A10,MATCH(MAX('Income Breakdown'!C6:C10),'Income Breakdown'!C6:C10,0))</f>
+        <v>Sales Revenue</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <f aca="false">MAX('Income Breakdown'!C6:C10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="10" t="str">
+        <f aca="false">INDEX('Expense Breakdown'!A6:A14,MATCH(MAX('Expense Breakdown'!C6:C14),'Expense Breakdown'!C6:C14,0))</f>
+        <v>Cost of Goods</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <f aca="false">MAX('Expense Breakdown'!C6:C14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" s="22" t="n">
+        <f aca="false">MIN(MAX(C6/0.3,0),1)*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="22" t="n">
+        <f aca="false">MIN(MAX((D6+0.2)/0.4,0),1)*100</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="22" t="n">
+        <f aca="false">MIN(MAX(E6/6,0),1)*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <f aca="false">AVERAGE(B19:B21)</f>
+        <v>16.6666666666667</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A24:C24"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="1" minLength="10" maxLength="90">
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF4C7A47"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BE77E0F8-A071-45A4-B9A5-C6805DE718A2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{BE77E0F8-A071-45A4-B9A5-C6805DE718A2}">
+            <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FF4C7A47"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B10</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -8866,7 +10218,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8878,7 +10230,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8890,13 +10242,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>2026</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>1</v>
@@ -8904,19 +10256,19 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8943,36 +10295,36 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Sales Revenue",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
         <v>0</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E11" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Cost of Goods",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
@@ -8981,14 +10333,14 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Shipping Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
         <v>0</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Shipping Costs",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
@@ -8997,14 +10349,14 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Custom Orders",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
         <v>0</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Marketing",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
@@ -9013,14 +10365,14 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Wholesale",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
         <v>0</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Software &amp; Tools",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
@@ -9029,14 +10381,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Other Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
         <v>0</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Fees &amp; Commissions",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
@@ -9045,7 +10397,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Office Supplies",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
@@ -9054,7 +10406,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Rent",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
@@ -9063,7 +10415,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Utilities",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
@@ -9072,7 +10424,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Other Expense",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
@@ -9081,20 +10433,20 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="B26" s="9" t="n">
         <f aca="false">A6</f>
@@ -9103,7 +10455,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B27" s="9" t="n">
         <f aca="false">B6</f>
@@ -9132,7 +10484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9145,7 +10497,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9157,7 +10509,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -9169,13 +10521,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>2026</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>1</v>
@@ -9183,19 +10535,19 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9222,26 +10574,26 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,"&gt;="&amp;((1-1)*3+1),Transactions!$H$3:$H$102,"&lt;="&amp;(((1-1)*3+1)+2))</f>
@@ -9258,7 +10610,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,"&gt;="&amp;((2-1)*3+1),Transactions!$H$3:$H$102,"&lt;="&amp;(((2-1)*3+1)+2))</f>
@@ -9275,7 +10627,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,"&gt;="&amp;((3-1)*3+1),Transactions!$H$3:$H$102,"&lt;="&amp;(((3-1)*3+1)+2))</f>
@@ -9292,7 +10644,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,"&gt;="&amp;((4-1)*3+1),Transactions!$H$3:$H$102,"&lt;="&amp;(((4-1)*3+1)+2))</f>
@@ -9329,7 +10681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9342,7 +10694,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9354,7 +10706,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -9366,7 +10718,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>2026</v>
@@ -9374,19 +10726,19 @@
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9413,32 +10765,32 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="B11" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,1)</f>
@@ -9463,7 +10815,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="B12" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,2)</f>
@@ -9488,7 +10840,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,3)</f>
@@ -9513,7 +10865,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B14" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,4)</f>
@@ -9538,7 +10890,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B15" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,5)</f>
@@ -9563,7 +10915,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="B16" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,6)</f>
@@ -9588,7 +10940,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="B17" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,7)</f>
@@ -9613,7 +10965,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="B18" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,8)</f>
@@ -9638,7 +10990,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,9)</f>
@@ -9663,7 +11015,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,10)</f>
@@ -9688,7 +11040,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B21" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,11)</f>
@@ -9713,7 +11065,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,12)</f>
@@ -9741,6 +11093,29 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
+  <conditionalFormatting sqref="D11:D22">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="1" minLength="10" maxLength="90">
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FF4C7A47"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{61972E6A-54CA-4D89-A4EA-A9173BDBF0C7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11:F22">
+    <cfRule type="iconSet" priority="3">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9749,10 +11124,27 @@
     <oddFooter/>
   </headerFooter>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{61972E6A-54CA-4D89-A4EA-A9173BDBF0C7}">
+            <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:negativeFillColor rgb="FF4C7A47"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D11:D22</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9765,7 +11157,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9777,7 +11169,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -9789,7 +11181,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -9799,20 +11191,20 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="26" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A6</f>
         <v>2024</v>
       </c>
@@ -9830,7 +11222,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="26" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A7</f>
         <v>2025</v>
       </c>
@@ -9848,7 +11240,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="26" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A8</f>
         <v>2026</v>
       </c>
@@ -9866,7 +11258,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="26" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A9</f>
         <v>2027</v>
       </c>
@@ -9884,7 +11276,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="26" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A10</f>
         <v>2028</v>
       </c>
@@ -9903,21 +11295,21 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9955,7 +11347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -9968,7 +11360,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9980,7 +11372,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -9992,7 +11384,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>2026</v>
@@ -10000,18 +11392,18 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Sales Revenue")</f>
@@ -10024,7 +11416,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Shipping Income")</f>
@@ -10037,7 +11429,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Custom Orders")</f>
@@ -10050,7 +11442,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Wholesale")</f>
@@ -10063,7 +11455,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" s="9" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$C$3:$C$102,"Other Income")</f>
@@ -10079,6 +11471,20 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6:C10">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="1" minLength="10" maxLength="90">
+        <cfvo type="min" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FF4C7A47"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{AC403CBD-DBE9-4841-A75F-9984AB843A51}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -10087,192 +11493,22 @@
     <oddFooter/>
   </headerFooter>
   <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Cost of Goods")</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Cost of Goods",Transactions!$G$3:$G$102,$B$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Shipping Costs")</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Shipping Costs",Transactions!$G$3:$G$102,$B$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Marketing")</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Marketing",Transactions!$G$3:$G$102,$B$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Software &amp; Tools")</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Software &amp; Tools",Transactions!$G$3:$G$102,$B$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Fees &amp; Commissions")</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Fees &amp; Commissions",Transactions!$G$3:$G$102,$B$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Office Supplies")</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Office Supplies",Transactions!$G$3:$G$102,$B$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Rent")</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Rent",Transactions!$G$3:$G$102,$B$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Utilities")</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Utilities",Transactions!$G$3:$G$102,$B$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Other Expense")</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$C$3:$C$102,"Other Expense",Transactions!$G$3:$G$102,$B$3)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{AC403CBD-DBE9-4841-A75F-9984AB843A51}">
+            <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:negativeFillColor rgb="FF4C7A47"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>B6:C10</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/bookkeeping_template.xlsx
+++ b/bookkeeping_template.xlsx
@@ -486,7 +486,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,8 +564,39 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="12"/>
+      <color rgb="FFC9DFC2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF1F3B21"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FF1F3B21"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -574,13 +605,6 @@
       <b val="true"/>
       <sz val="14"/>
       <color rgb="FF2F5233"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -606,7 +630,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -616,7 +640,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5233"/>
-        <bgColor rgb="FF555555"/>
+        <bgColor rgb="FF1F3B21"/>
       </patternFill>
     </fill>
     <fill>
@@ -627,18 +651,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4C7A47"/>
-        <bgColor rgb="FF555555"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF5EC"/>
-        <bgColor rgb="FFEAF7EC"/>
+        <fgColor rgb="FFDCEAD5"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -658,6 +676,67 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF4C7A47"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF4C7A47"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF2F5233"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF4C7A47"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color rgb="FF4C7A47"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4C7A47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF4C7A47"/>
       </bottom>
       <diagonal/>
     </border>
@@ -687,7 +766,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -748,28 +827,44 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -780,16 +875,28 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -804,15 +911,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -865,7 +980,7 @@
       <rgbColor rgb="FFEAF7EC"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFDC853E"/>
-      <rgbColor rgb="FF4672A8"/>
+      <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -873,32 +988,32 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF6E9B5E"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFEFF5EC"/>
-      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFDEEEE"/>
+      <rgbColor rgb="FFDCEAD5"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FFB8CD97"/>
       <rgbColor rgb="FFD09493"/>
       <rgbColor rgb="FF8064A2"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF4A7EBB"/>
+      <rgbColor rgb="FFC9DFC2"/>
+      <rgbColor rgb="FF4672A8"/>
       <rgbColor rgb="FF4BACC6"/>
       <rgbColor rgb="FF9BBB59"/>
-      <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FF8AA64F"/>
+      <rgbColor rgb="FFC9A227"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF725990"/>
       <rgbColor rgb="FF888888"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF4299B0"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF2F5233"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FFC0504D"/>
       <rgbColor rgb="FF555555"/>
-      <rgbColor rgb="FF2F5233"/>
+      <rgbColor rgb="FF1F3B21"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1032,12 +1147,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -1056,12 +1172,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -1080,12 +1197,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -1104,12 +1222,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -1128,12 +1247,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
@@ -1150,12 +1270,13 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:separator>; </c:separator>
+            <c:separator>
+</c:separator>
             <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
@@ -1317,10 +1438,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -1441,11 +1564,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="44485420"/>
-        <c:axId val="26811196"/>
+        <c:axId val="34238565"/>
+        <c:axId val="26360375"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="44485420"/>
+        <c:axId val="34238565"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1477,7 +1600,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26811196"/>
+        <c:crossAx val="26360375"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1485,7 +1608,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26811196"/>
+        <c:axId val="26360375"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1561,7 +1684,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44485420"/>
+        <c:crossAx val="34238565"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1673,11 +1796,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="2f5233"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1809,11 +1932,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="21007547"/>
-        <c:axId val="89725098"/>
+        <c:axId val="70428427"/>
+        <c:axId val="79513881"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21007547"/>
+        <c:axId val="70428427"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1845,7 +1968,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89725098"/>
+        <c:crossAx val="79513881"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1853,7 +1976,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89725098"/>
+        <c:axId val="79513881"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1895,7 +2018,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21007547"/>
+        <c:crossAx val="70428427"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2119,12 +2242,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -2143,12 +2267,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -2167,12 +2292,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -2191,12 +2317,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -2215,12 +2342,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="5"/>
@@ -2239,12 +2367,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="6"/>
@@ -2263,12 +2392,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="7"/>
@@ -2287,12 +2417,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="8"/>
@@ -2311,12 +2442,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
@@ -2333,12 +2465,13 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:separator>; </c:separator>
+            <c:separator>
+</c:separator>
             <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
@@ -2524,10 +2657,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -2588,11 +2723,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="55475747"/>
-        <c:axId val="91034759"/>
+        <c:axId val="28137881"/>
+        <c:axId val="75531702"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="55475747"/>
+        <c:axId val="28137881"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2624,7 +2759,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91034759"/>
+        <c:crossAx val="75531702"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2632,7 +2767,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91034759"/>
+        <c:axId val="75531702"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2708,7 +2843,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55475747"/>
+        <c:crossAx val="28137881"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2821,10 +2956,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -2911,10 +3048,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c0504d"/>
+              <a:srgbClr val="6e9b5e"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="6e9b5e"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -3001,10 +3140,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="9bbb59"/>
+              <a:srgbClr val="c9a227"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="c9a227"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -3077,11 +3218,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="41076862"/>
-        <c:axId val="57819110"/>
+        <c:axId val="81992659"/>
+        <c:axId val="84947443"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41076862"/>
+        <c:axId val="81992659"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3113,7 +3254,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57819110"/>
+        <c:crossAx val="84947443"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3121,7 +3262,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57819110"/>
+        <c:axId val="84947443"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3197,7 +3338,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41076862"/>
+        <c:crossAx val="81992659"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3310,10 +3451,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -3434,11 +3577,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="51836746"/>
-        <c:axId val="28599433"/>
+        <c:axId val="29130294"/>
+        <c:axId val="96242591"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="51836746"/>
+        <c:axId val="29130294"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3470,7 +3613,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28599433"/>
+        <c:crossAx val="96242591"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3478,7 +3621,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28599433"/>
+        <c:axId val="96242591"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3554,7 +3697,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51836746"/>
+        <c:crossAx val="29130294"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3667,10 +3810,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="2f5233"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -3763,10 +3908,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="c0504d"/>
+              <a:srgbClr val="6e9b5e"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="6e9b5e"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -3859,10 +4006,12 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="9bbb59"/>
+              <a:srgbClr val="c9a227"/>
             </a:solidFill>
             <a:ln w="0">
-              <a:noFill/>
+              <a:solidFill>
+                <a:srgbClr val="c9a227"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
@@ -3941,11 +4090,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="85555836"/>
-        <c:axId val="11949451"/>
+        <c:axId val="17582932"/>
+        <c:axId val="95219845"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85555836"/>
+        <c:axId val="17582932"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3977,7 +4126,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11949451"/>
+        <c:crossAx val="95219845"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3985,7 +4134,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11949451"/>
+        <c:axId val="95219845"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4061,7 +4210,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85555836"/>
+        <c:crossAx val="17582932"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4241,12 +4390,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -4265,12 +4415,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -4289,12 +4440,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -4313,12 +4465,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -4337,12 +4490,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
@@ -4359,12 +4513,13 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:separator>; </c:separator>
+            <c:separator>
+</c:separator>
             <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
@@ -4637,12 +4792,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -4661,12 +4817,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -4685,12 +4842,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -4709,12 +4867,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -4733,12 +4892,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="5"/>
@@ -4757,12 +4917,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="6"/>
@@ -4781,12 +4942,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="7"/>
@@ -4805,12 +4967,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="8"/>
@@ -4829,12 +4992,13 @@
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="1"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="1"/>
-              <c:showSerName val="1"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
               <c:showPercent val="1"/>
-              <c:separator>; </c:separator>
+              <c:separator>
+</c:separator>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="square"/>
@@ -4851,12 +5015,13 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="1"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="1"/>
-            <c:separator>; </c:separator>
+            <c:separator>
+</c:separator>
             <c:showLeaderLines val="1"/>
           </c:dLbls>
           <c:cat>
@@ -5041,11 +5206,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4a7ebb"/>
+              <a:srgbClr val="2f5233"/>
             </a:solidFill>
             <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="4a7ebb"/>
+                <a:srgbClr val="2f5233"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -5165,11 +5330,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="60078730"/>
-        <c:axId val="59511018"/>
+        <c:axId val="38824811"/>
+        <c:axId val="46002470"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="60078730"/>
+        <c:axId val="38824811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5201,7 +5366,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59511018"/>
+        <c:crossAx val="46002470"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5209,7 +5374,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59511018"/>
+        <c:axId val="46002470"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5251,7 +5416,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60078730"/>
+        <c:crossAx val="38824811"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5309,14 +5474,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>204480</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>28800</xdr:rowOff>
+      <xdr:rowOff>43200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5324,7 +5489,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9601200" y="1800360"/>
+        <a:off x="9601200" y="2104920"/>
         <a:ext cx="3239640" cy="2519640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5339,14 +5504,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>204480</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>28800</xdr:rowOff>
+      <xdr:rowOff>43200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5354,7 +5519,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="14913000" y="1800360"/>
+        <a:off x="14913000" y="2104920"/>
         <a:ext cx="3239640" cy="2519640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5369,14 +5534,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>204480</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>28440</xdr:rowOff>
+      <xdr:rowOff>43200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5384,7 +5549,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9601200" y="4657680"/>
+        <a:off x="9601200" y="4962600"/>
         <a:ext cx="3239640" cy="2519640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5404,14 +5569,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>126720</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5419,7 +5584,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7112160" y="1800360"/>
+        <a:off x="7112160" y="2104920"/>
         <a:ext cx="4679640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5439,14 +5604,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>447840</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5454,7 +5619,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8226360" y="1800360"/>
+        <a:off x="8226360" y="2104920"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5474,14 +5639,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>49320</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>122760</xdr:rowOff>
+      <xdr:rowOff>108720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5489,7 +5654,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6093000" y="762120"/>
+        <a:off x="6093000" y="1038240"/>
         <a:ext cx="6119640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5509,14 +5674,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>525600</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>177120</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5524,7 +5689,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6093000" y="762120"/>
+        <a:off x="6093000" y="1038240"/>
         <a:ext cx="4319640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5544,14 +5709,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>525600</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>177120</xdr:rowOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5559,7 +5724,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6093000" y="762120"/>
+        <a:off x="6093000" y="1038240"/>
         <a:ext cx="4319640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5579,14 +5744,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>447840</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>58320</xdr:rowOff>
+      <xdr:rowOff>72720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5594,7 +5759,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9334440" y="762120"/>
+        <a:off x="9334440" y="1038240"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5614,14 +5779,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>486720</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5629,7 +5794,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3603600" y="762120"/>
+        <a:off x="3603600" y="1038240"/>
         <a:ext cx="5039640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -5649,14 +5814,14 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>447840</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>18000</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5664,7 +5829,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7870680" y="2562120"/>
+        <a:off x="7870680" y="2867040"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6018,46 +6183,46 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="17" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="24" t="s">
         <v>107</v>
       </c>
     </row>
@@ -6192,7 +6357,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A572D43F-A089-4310-AEED-F4F2A5D9BCDF}</x14:id>
+          <x14:id>{D8F01B49-602A-4336-B5F4-13E0BBB8CD47}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -6209,7 +6374,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A572D43F-A089-4310-AEED-F4F2A5D9BCDF}">
+          <x14:cfRule type="dataBar" id="{D8F01B49-602A-4336-B5F4-13E0BBB8CD47}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -6236,61 +6401,61 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="17" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="34" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="24" t="s">
         <v>49</v>
       </c>
     </row>
@@ -6311,7 +6476,7 @@
         <f aca="false">B6-C6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="35" t="n">
         <f aca="false">IFERROR(D6/B6,0)</f>
         <v>0</v>
       </c>
@@ -6341,7 +6506,7 @@
         <f aca="false">B7-C7</f>
         <v>0</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="35" t="n">
         <f aca="false">IFERROR(D7/B7,0)</f>
         <v>0</v>
       </c>
@@ -6349,7 +6514,7 @@
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A7)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="28" t="n">
+      <c r="G7" s="35" t="n">
         <f aca="false">IFERROR((B7-B6)/B6,0)</f>
         <v>0</v>
       </c>
@@ -6371,7 +6536,7 @@
         <f aca="false">B8-C8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="35" t="n">
         <f aca="false">IFERROR(D8/B8,0)</f>
         <v>0</v>
       </c>
@@ -6379,7 +6544,7 @@
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A8)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="35" t="n">
         <f aca="false">IFERROR((B8-B7)/B7,0)</f>
         <v>0</v>
       </c>
@@ -6401,7 +6566,7 @@
         <f aca="false">B9-C9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="28" t="n">
+      <c r="E9" s="35" t="n">
         <f aca="false">IFERROR(D9/B9,0)</f>
         <v>0</v>
       </c>
@@ -6409,7 +6574,7 @@
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A9)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="35" t="n">
         <f aca="false">IFERROR((B9-B8)/B8,0)</f>
         <v>0</v>
       </c>
@@ -6431,7 +6596,7 @@
         <f aca="false">B10-C10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="E10" s="35" t="n">
         <f aca="false">IFERROR(D10/B10,0)</f>
         <v>0</v>
       </c>
@@ -6439,7 +6604,7 @@
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A10)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="35" t="n">
         <f aca="false">IFERROR((B10-B9)/B9,0)</f>
         <v>0</v>
       </c>
@@ -6461,7 +6626,7 @@
         <f aca="false">B11-C11</f>
         <v>0</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="35" t="n">
         <f aca="false">IFERROR(D11/B11,0)</f>
         <v>0</v>
       </c>
@@ -6469,7 +6634,7 @@
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A11)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="28" t="n">
+      <c r="G11" s="35" t="n">
         <f aca="false">IFERROR((B11-B10)/B10,0)</f>
         <v>0</v>
       </c>
@@ -6491,7 +6656,7 @@
         <f aca="false">B12-C12</f>
         <v>0</v>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="E12" s="35" t="n">
         <f aca="false">IFERROR(D12/B12,0)</f>
         <v>0</v>
       </c>
@@ -6499,7 +6664,7 @@
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A12)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="35" t="n">
         <f aca="false">IFERROR((B12-B11)/B11,0)</f>
         <v>0</v>
       </c>
@@ -6521,7 +6686,7 @@
         <f aca="false">B13-C13</f>
         <v>0</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="35" t="n">
         <f aca="false">IFERROR(D13/B13,0)</f>
         <v>0</v>
       </c>
@@ -6529,7 +6694,7 @@
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A13)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="35" t="n">
         <f aca="false">IFERROR((B13-B12)/B12,0)</f>
         <v>0</v>
       </c>
@@ -6551,7 +6716,7 @@
         <f aca="false">B14-C14</f>
         <v>0</v>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="35" t="n">
         <f aca="false">IFERROR(D14/B14,0)</f>
         <v>0</v>
       </c>
@@ -6559,7 +6724,7 @@
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="35" t="n">
         <f aca="false">IFERROR((B14-B13)/B13,0)</f>
         <v>0</v>
       </c>
@@ -6581,7 +6746,7 @@
         <f aca="false">B15-C15</f>
         <v>0</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="35" t="n">
         <f aca="false">IFERROR(D15/B15,0)</f>
         <v>0</v>
       </c>
@@ -6589,7 +6754,7 @@
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,A15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="35" t="n">
         <f aca="false">IFERROR((B15-B14)/B14,0)</f>
         <v>0</v>
       </c>
@@ -6633,43 +6798,43 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="17" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="24" t="s">
         <v>113</v>
       </c>
     </row>
@@ -6782,10 +6947,10 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="37" t="n">
         <f aca="false">SUM(B6:B17)</f>
         <v>0</v>
       </c>
@@ -6817,47 +6982,59 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="18" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="n">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="n">
         <f aca="false">Setup!$B$7</f>
         <v>0</v>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="20" t="n">
         <f aca="false">Setup!$B$7+SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income")-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense")</f>
         <v>0</v>
       </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
@@ -6868,9 +7045,9 @@
       <c r="A8" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B8" s="31" t="n">
+      <c r="B8" s="38" t="n">
         <f aca="true">TODAY()</f>
-        <v>46248</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6891,10 +7068,10 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="37" t="n">
         <f aca="false">B9-B10</f>
         <v>0</v>
       </c>
@@ -6906,15 +7083,15 @@
       <c r="C13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="39" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="24" t="s">
         <v>125</v>
       </c>
     </row>
@@ -7090,7 +7267,7 @@
       <c r="A3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="40" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7983,7 +8160,7 @@
       <c r="A4" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="25" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7991,7 +8168,7 @@
       <c r="A5" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="25" t="s">
         <v>135</v>
       </c>
     </row>
@@ -7999,7 +8176,7 @@
       <c r="A6" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="25" t="s">
         <v>137</v>
       </c>
     </row>
@@ -8007,7 +8184,7 @@
       <c r="A7" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="25" t="s">
         <v>139</v>
       </c>
     </row>
@@ -8015,7 +8192,7 @@
       <c r="A8" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="25" t="s">
         <v>141</v>
       </c>
     </row>
@@ -8023,7 +8200,7 @@
       <c r="A9" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="25" t="s">
         <v>143</v>
       </c>
     </row>
@@ -8031,7 +8208,7 @@
       <c r="A10" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="25" t="s">
         <v>145</v>
       </c>
     </row>
@@ -9969,76 +10146,82 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="17"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="17" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="18" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="n">
         <f aca="false">'Account Balance'!B4</f>
         <v>0</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3)-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$G$3:$G$102,$B$3)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="21" t="n">
         <f aca="false">IFERROR(B6/SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3),0)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="21" t="n">
         <f aca="false">IFERROR((SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3)-SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3-1))/SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3-1),0)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="22" t="n">
         <f aca="false">IFERROR(A6/(SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$G$3:$G$102,$B$3)/12),0)</f>
         <v>0</v>
       </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -10049,7 +10232,7 @@
       <c r="A10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="23" t="n">
         <f aca="false">IFERROR(B6/Setup!$B$6,0)</f>
         <v>0</v>
       </c>
@@ -10060,11 +10243,11 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="24" t="s">
         <v>40</v>
       </c>
     </row>
@@ -10100,47 +10283,47 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B19" s="26" t="n">
         <f aca="false">MIN(MAX(C6/0.3,0),1)*100</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B20" s="26" t="n">
         <f aca="false">MIN(MAX((D6+0.2)/0.4,0),1)*100</f>
         <v>50</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B21" s="26" t="n">
         <f aca="false">MIN(MAX(E6/6,0),1)*100</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="24" t="n">
+      <c r="B22" s="28" t="n">
         <f aca="false">AVERAGE(B19:B21)</f>
         <v>16.6666666666667</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -10157,7 +10340,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BE77E0F8-A071-45A4-B9A5-C6805DE718A2}</x14:id>
+          <x14:id>{FC1B82F5-5F90-4199-B0D2-A9BB1366CA9F}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10185,7 +10368,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BE77E0F8-A071-45A4-B9A5-C6805DE718A2}">
+          <x14:cfRule type="dataBar" id="{FC1B82F5-5F90-4199-B0D2-A9BB1366CA9F}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -10216,82 +10399,88 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="30" t="n">
         <v>2026</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="32" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="20" t="n">
         <f aca="false">A6-B6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="21" t="n">
         <f aca="false">IFERROR(C6/A6,0)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,$D$3)</f>
         <v>0</v>
       </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -10302,16 +10491,16 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="24" t="s">
         <v>70</v>
       </c>
     </row>
@@ -10437,10 +10626,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="24" t="s">
         <v>70</v>
       </c>
     </row>
@@ -10495,82 +10684,88 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="30" t="n">
         <v>2026</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="32" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,"&gt;="&amp;(($D$3-1)*3+1),Transactions!$H$3:$H$102,"&lt;="&amp;((($D$3-1)*3+1)+2))</f>
         <v>0</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,"&gt;="&amp;(($D$3-1)*3+1),Transactions!$H$3:$H$102,"&lt;="&amp;((($D$3-1)*3+1)+2))</f>
         <v>0</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="20" t="n">
         <f aca="false">A6-B6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="21" t="n">
         <f aca="false">IFERROR(C6/A6,0)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3,Transactions!$H$3:$H$102,"&gt;="&amp;(($D$3-1)*3+1),Transactions!$H$3:$H$102,"&lt;="&amp;((($D$3-1)*3+1)+2))</f>
         <v>0</v>
       </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -10578,16 +10773,16 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="24" t="s">
         <v>78</v>
       </c>
     </row>
@@ -10692,76 +10887,82 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="17" t="n">
         <v>2026</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Income",Transactions!$G$3:$G$102,$B$3)</f>
         <v>0</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$E$3:$E$102,Transactions!$B$3:$B$102,"Expense",Transactions!$G$3:$G$102,$B$3)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="20" t="n">
         <f aca="false">A6-B6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="21" t="n">
         <f aca="false">IFERROR(C6/A6,0)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">SUMIFS(Transactions!$F$3:$F$102,Transactions!$G$3:$G$102,$B$3)</f>
         <v>0</v>
       </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
@@ -10769,22 +10970,22 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="24" t="s">
         <v>86</v>
       </c>
     </row>
@@ -11102,7 +11303,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61972E6A-54CA-4D89-A4EA-A9173BDBF0C7}</x14:id>
+          <x14:id>{2BF06D1F-18BC-40C1-A931-5E8C7CF05946}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11128,7 +11329,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{61972E6A-54CA-4D89-A4EA-A9173BDBF0C7}">
+          <x14:cfRule type="dataBar" id="{2BF06D1F-18BC-40C1-A931-5E8C7CF05946}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -11155,29 +11356,29 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -11190,21 +11391,21 @@
       <c r="F3" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="24" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="33" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A6</f>
         <v>2024</v>
       </c>
@@ -11222,7 +11423,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="33" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A7</f>
         <v>2025</v>
       </c>
@@ -11240,7 +11441,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="33" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A8</f>
         <v>2026</v>
       </c>
@@ -11258,7 +11459,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="33" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A9</f>
         <v>2027</v>
       </c>
@@ -11276,7 +11477,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="33" t="n">
         <f aca="false">'Profit &amp; Loss Summary'!A10</f>
         <v>2028</v>
       </c>
@@ -11298,37 +11499,45 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="18" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="n">
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="n">
         <f aca="false">SUM(B6:B10)</f>
         <v>0</v>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="20" t="n">
         <f aca="false">SUM(C6:C10)</f>
         <v>0</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="20" t="n">
         <f aca="false">SUM(D6:D10)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="20" t="n">
         <f aca="false">AVERAGE(D6:D10)</f>
         <v>0</v>
       </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -11358,46 +11567,46 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="17" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="24" t="s">
         <v>107</v>
       </c>
     </row>
@@ -11480,7 +11689,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AC403CBD-DBE9-4841-A75F-9984AB843A51}</x14:id>
+          <x14:id>{742BD646-9419-4988-B290-6F744FFFA17B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11497,7 +11706,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AC403CBD-DBE9-4841-A75F-9984AB843A51}">
+          <x14:cfRule type="dataBar" id="{742BD646-9419-4988-B290-6F744FFFA17B}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
